--- a/artfynd/A 25270-2025 artfynd.xlsx
+++ b/artfynd/A 25270-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129299189</v>
       </c>
       <c r="B2" t="n">
-        <v>92876</v>
+        <v>92881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129299186</v>
       </c>
       <c r="B3" t="n">
-        <v>92900</v>
+        <v>92905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129299185</v>
       </c>
       <c r="B4" t="n">
-        <v>92900</v>
+        <v>92905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>129299190</v>
       </c>
       <c r="B5" t="n">
-        <v>92900</v>
+        <v>92905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129299192</v>
       </c>
       <c r="B6" t="n">
-        <v>92367</v>
+        <v>92372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25270-2025 artfynd.xlsx
+++ b/artfynd/A 25270-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129299189</v>
       </c>
       <c r="B2" t="n">
-        <v>92881</v>
+        <v>92882</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129299186</v>
       </c>
       <c r="B3" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129299185</v>
       </c>
       <c r="B4" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>129299190</v>
       </c>
       <c r="B5" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129299192</v>
       </c>
       <c r="B6" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25270-2025 artfynd.xlsx
+++ b/artfynd/A 25270-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129299189</v>
       </c>
       <c r="B2" t="n">
-        <v>92882</v>
+        <v>92887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129299186</v>
       </c>
       <c r="B3" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129299185</v>
       </c>
       <c r="B4" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>129299190</v>
       </c>
       <c r="B5" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129299192</v>
       </c>
       <c r="B6" t="n">
-        <v>92373</v>
+        <v>92378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25270-2025 artfynd.xlsx
+++ b/artfynd/A 25270-2025 artfynd.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Aivars Dunskis, Julia Stigenberg</t>
+          <t>Julia Stigenberg, Aivars Dunskis</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Aivars Dunskis, Julia Stigenberg</t>
+          <t>Julia Stigenberg, Aivars Dunskis</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Aivars Dunskis, Julia Stigenberg</t>
+          <t>Julia Stigenberg, Aivars Dunskis</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Aivars Dunskis, Julia Stigenberg</t>
+          <t>Julia Stigenberg, Aivars Dunskis</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Aivars Dunskis, Julia Stigenberg</t>
+          <t>Julia Stigenberg, Aivars Dunskis</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 25270-2025 artfynd.xlsx
+++ b/artfynd/A 25270-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129299189</v>
       </c>
       <c r="B2" t="n">
-        <v>92887</v>
+        <v>92891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Julia Stigenberg, Aivars Dunskis</t>
+          <t>Aivars Dunskis, Julia Stigenberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>129299186</v>
       </c>
       <c r="B3" t="n">
-        <v>92911</v>
+        <v>92915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Julia Stigenberg, Aivars Dunskis</t>
+          <t>Aivars Dunskis, Julia Stigenberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -880,7 +880,7 @@
         <v>129299185</v>
       </c>
       <c r="B4" t="n">
-        <v>92911</v>
+        <v>92915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Julia Stigenberg, Aivars Dunskis</t>
+          <t>Aivars Dunskis, Julia Stigenberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -985,7 +985,7 @@
         <v>129299190</v>
       </c>
       <c r="B5" t="n">
-        <v>92911</v>
+        <v>92915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Julia Stigenberg, Aivars Dunskis</t>
+          <t>Aivars Dunskis, Julia Stigenberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
         <v>129299192</v>
       </c>
       <c r="B6" t="n">
-        <v>92378</v>
+        <v>92382</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Julia Stigenberg, Aivars Dunskis</t>
+          <t>Aivars Dunskis, Julia Stigenberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 25270-2025 artfynd.xlsx
+++ b/artfynd/A 25270-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129299189</v>
       </c>
       <c r="B2" t="n">
-        <v>92891</v>
+        <v>92893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129299186</v>
       </c>
       <c r="B3" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129299185</v>
       </c>
       <c r="B4" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>129299190</v>
       </c>
       <c r="B5" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129299192</v>
       </c>
       <c r="B6" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25270-2025 artfynd.xlsx
+++ b/artfynd/A 25270-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129299189</v>
       </c>
       <c r="B2" t="n">
-        <v>92893</v>
+        <v>92896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129299186</v>
       </c>
       <c r="B3" t="n">
-        <v>92917</v>
+        <v>92920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129299185</v>
       </c>
       <c r="B4" t="n">
-        <v>92917</v>
+        <v>92920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>129299190</v>
       </c>
       <c r="B5" t="n">
-        <v>92917</v>
+        <v>92920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129299192</v>
       </c>
       <c r="B6" t="n">
-        <v>92384</v>
+        <v>92387</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25270-2025 artfynd.xlsx
+++ b/artfynd/A 25270-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129299189</v>
       </c>
       <c r="B2" t="n">
-        <v>92896</v>
+        <v>92899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129299186</v>
       </c>
       <c r="B3" t="n">
-        <v>92920</v>
+        <v>92923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129299185</v>
       </c>
       <c r="B4" t="n">
-        <v>92920</v>
+        <v>92923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>129299190</v>
       </c>
       <c r="B5" t="n">
-        <v>92920</v>
+        <v>92923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129299192</v>
       </c>
       <c r="B6" t="n">
-        <v>92387</v>
+        <v>92390</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25270-2025 artfynd.xlsx
+++ b/artfynd/A 25270-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129299189</v>
       </c>
       <c r="B2" t="n">
-        <v>92899</v>
+        <v>92900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129299186</v>
       </c>
       <c r="B3" t="n">
-        <v>92923</v>
+        <v>92924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129299185</v>
       </c>
       <c r="B4" t="n">
-        <v>92923</v>
+        <v>92924</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>129299190</v>
       </c>
       <c r="B5" t="n">
-        <v>92923</v>
+        <v>92924</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129299192</v>
       </c>
       <c r="B6" t="n">
-        <v>92390</v>
+        <v>92391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25270-2025 artfynd.xlsx
+++ b/artfynd/A 25270-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129299189</v>
       </c>
       <c r="B2" t="n">
-        <v>92900</v>
+        <v>92917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129299186</v>
       </c>
       <c r="B3" t="n">
-        <v>92924</v>
+        <v>92941</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129299185</v>
       </c>
       <c r="B4" t="n">
-        <v>92924</v>
+        <v>92941</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>129299190</v>
       </c>
       <c r="B5" t="n">
-        <v>92924</v>
+        <v>92941</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129299192</v>
       </c>
       <c r="B6" t="n">
-        <v>92391</v>
+        <v>92408</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
